--- a/data/trans_dic/IP18_E_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18_E_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,69; 97,66</t>
+          <t>90,88; 97,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,77; 96,16</t>
+          <t>88,08; 96,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,39; 96,19</t>
+          <t>88,86; 96,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64,92; 93,49</t>
+          <t>65,41; 92,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,45; 93,72</t>
+          <t>83,43; 93,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,0; 97,84</t>
+          <t>91,56; 97,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,67; 95,57</t>
+          <t>87,69; 95,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,44; 100,0</t>
+          <t>86,86; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88,34; 94,69</t>
+          <t>88,58; 94,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91,7; 96,09</t>
+          <t>91,63; 96,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89,91; 95,1</t>
+          <t>89,8; 95,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,07; 96,03</t>
+          <t>79,75; 95,88</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,84; 95,19</t>
+          <t>90,16; 95,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,25; 97,96</t>
+          <t>93,42; 97,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,81; 96,87</t>
+          <t>91,67; 96,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,04; 95,25</t>
+          <t>75,18; 95,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,84; 95,73</t>
+          <t>90,78; 96,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,6; 96,97</t>
+          <t>92,68; 97,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,25; 96,78</t>
+          <t>92,26; 96,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>76,23; 94,85</t>
+          <t>74,9; 95,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91,42; 95,08</t>
+          <t>91,36; 95,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93,86; 96,95</t>
+          <t>93,9; 97,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92,82; 96,27</t>
+          <t>92,83; 96,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,42; 93,5</t>
+          <t>78,44; 93,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,77; 96,48</t>
+          <t>88,76; 96,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,55; 97,18</t>
+          <t>90,69; 97,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,52; 95,91</t>
+          <t>89,69; 95,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53,77; 90,01</t>
+          <t>56,19; 91,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,64; 97,17</t>
+          <t>89,57; 97,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,55; 96,03</t>
+          <t>89,21; 96,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,3; 97,04</t>
+          <t>91,7; 97,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91,59; 100,0</t>
+          <t>92,69; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,81; 96,28</t>
+          <t>90,93; 96,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91,3; 96,07</t>
+          <t>91,24; 96,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91,71; 95,88</t>
+          <t>91,62; 95,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,36; 95,03</t>
+          <t>74,48; 94,96</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,0; 96,3</t>
+          <t>89,77; 96,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91,1; 96,97</t>
+          <t>91,38; 96,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,39; 97,33</t>
+          <t>90,81; 97,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75,28; 97,16</t>
+          <t>76,43; 97,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,91; 96,42</t>
+          <t>89,89; 96,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,24; 97,18</t>
+          <t>91,31; 97,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,96; 96,57</t>
+          <t>89,68; 96,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>82,82; 97,96</t>
+          <t>84,11; 98,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,09; 95,72</t>
+          <t>90,89; 95,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,4; 96,33</t>
+          <t>91,94; 96,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91,53; 96,08</t>
+          <t>91,5; 96,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,68; 96,43</t>
+          <t>85,03; 96,1</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,89; 95,08</t>
+          <t>91,94; 94,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,15; 96,03</t>
+          <t>93,02; 96,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92,44; 95,38</t>
+          <t>92,38; 95,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,35; 89,42</t>
+          <t>73,68; 89,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>91,27; 94,52</t>
+          <t>91,21; 94,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,05; 95,87</t>
+          <t>92,94; 95,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,6; 95,5</t>
+          <t>92,6; 95,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>89,6; 96,71</t>
+          <t>89,59; 96,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92,03; 94,35</t>
+          <t>92,0; 94,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93,66; 95,71</t>
+          <t>93,75; 95,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92,98; 95,07</t>
+          <t>92,93; 95,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>84,51; 92,72</t>
+          <t>84,54; 92,72</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91282; 98298</t>
+          <t>91477; 98327</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>125614; 136061</t>
+          <t>124627; 135898</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113438; 122068</t>
+          <t>112766; 122169</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10578; 15234</t>
+          <t>10658; 15128</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>89324; 100316</t>
+          <t>89300; 100002</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>130527; 138806</t>
+          <t>129898; 138729</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>101842; 111012</t>
+          <t>101858; 110967</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16315; 18447</t>
+          <t>16023; 18447</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>183478; 196654</t>
+          <t>183962; 196465</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>259852; 272292</t>
+          <t>259643; 272747</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>218530; 231143</t>
+          <t>218265; 231054</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28164; 33361</t>
+          <t>27705; 33310</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>204390; 216565</t>
+          <t>205108; 217256</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>206745; 217178</t>
+          <t>207125; 216916</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>178848; 188718</t>
+          <t>178578; 188502</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21442; 26858</t>
+          <t>21200; 26793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>208515; 219747</t>
+          <t>208387; 220839</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>236900; 248077</t>
+          <t>237092; 248351</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>216785; 227428</t>
+          <t>216811; 227555</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25712; 31990</t>
+          <t>25262; 32130</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>417824; 434555</t>
+          <t>417551; 434318</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>448192; 462959</t>
+          <t>448418; 463446</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>398927; 413755</t>
+          <t>399001; 413955</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48563; 57900</t>
+          <t>48574; 57673</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91851; 99836</t>
+          <t>91840; 99872</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>136886; 146905</t>
+          <t>137085; 146837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>153342; 164292</t>
+          <t>153634; 163858</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16828; 28170</t>
+          <t>17585; 28505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>101151; 109645</t>
+          <t>101075; 109561</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>132210; 143364</t>
+          <t>133189; 143909</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>154612; 164334</t>
+          <t>155285; 164679</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33770; 36871</t>
+          <t>34174; 36871</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>196438; 208276</t>
+          <t>196700; 208321</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>274333; 288662</t>
+          <t>274141; 288620</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>312392; 326600</t>
+          <t>312107; 326304</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50007; 64779</t>
+          <t>50773; 64733</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>141624; 151529</t>
+          <t>141260; 151569</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>138143; 147044</t>
+          <t>138571; 147082</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>140560; 149698</t>
+          <t>139679; 149308</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18463; 23830</t>
+          <t>18745; 23902</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>147373; 158037</t>
+          <t>147326; 157767</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>150364; 160153</t>
+          <t>150487; 159875</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>132158; 143462</t>
+          <t>133232; 143484</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35237; 41679</t>
+          <t>35787; 41701</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>292642; 307499</t>
+          <t>291990; 306999</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>292401; 304817</t>
+          <t>290942; 304409</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>276754; 290509</t>
+          <t>276664; 290604</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57467; 64676</t>
+          <t>57028; 64455</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>541227; 559988</t>
+          <t>541509; 559492</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>620381; 639591</t>
+          <t>619523; 640023</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>597946; 616934</t>
+          <t>597539; 616918</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74582; 89702</t>
+          <t>73912; 89845</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>559770; 579694</t>
+          <t>559408; 579792</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>662339; 682374</t>
+          <t>661538; 682051</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>619551; 638985</t>
+          <t>619529; 638715</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>117908; 127257</t>
+          <t>117893; 127020</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1106523; 1134395</t>
+          <t>1106063; 1134911</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1290435; 1318748</t>
+          <t>1291657; 1317988</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1223471; 1251004</t>
+          <t>1222887; 1251511</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>195974; 215015</t>
+          <t>196061; 215028</t>
         </is>
       </c>
     </row>
